--- a/data/trans_bre/P32A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,24</t>
+          <t>-2,85; -0,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,03</t>
+          <t>-1,28; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,27</t>
+          <t>-1,92; 2,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,16</t>
+          <t>-2,15; 1,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 613,3</t>
+          <t>-75,19; 454,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 496,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,5</t>
+          <t>-100,0; 476,32</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; -0,33</t>
+          <t>-1,91; -0,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,35</t>
+          <t>-3,64; -0,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,21</t>
+          <t>-3,77; -0,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 4,48</t>
+          <t>-0,95; 4,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,35</t>
+          <t>-100,0; 51,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,92</t>
+          <t>-92,32; 21,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 472,41</t>
+          <t>-51,84; 416,21</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,09</t>
+          <t>-3,5; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; -1,89</t>
+          <t>-5,9; -2,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,06</t>
+          <t>-3,46; -0,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,73</t>
+          <t>-2,37; 2,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 159,69</t>
+          <t>-100,0; 352,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 67,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 481,75</t>
+          <t>-100,0; 380,13</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,52</t>
+          <t>-0,66; 1,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,12</t>
+          <t>-3,84; -0,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,09</t>
+          <t>-0,77; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,14</t>
+          <t>-3,08; 0,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,61; 33,08</t>
+          <t>-94,59; 20,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 350,26</t>
+          <t>-50,25; 396,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 31,78</t>
+          <t>-86,65; 25,67</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,16</t>
+          <t>-1,32; -0,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,69</t>
+          <t>-2,6; -0,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,33</t>
+          <t>-1,63; 0,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,77</t>
+          <t>-1,49; 0,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-92,29; -2,0</t>
+          <t>-93,63; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -29,94</t>
+          <t>-86,29; -24,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 24,37</t>
+          <t>-66,2; 21,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 53,64</t>
+          <t>-66,61; 50,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-45,39%</t>
+          <t>-46,43%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,39</t>
+          <t>-2,75; -0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 4,34</t>
+          <t>-1,38; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,48</t>
+          <t>-2,03; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,18</t>
+          <t>-2,13; 1,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 454,11</t>
+          <t>-73,83; 541,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 393,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 476,32</t>
+          <t>-100,0; 231,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>80,76%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; -0,33</t>
+          <t>-1,88; -0,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,64; -0,32</t>
+          <t>-3,6; -0,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,05</t>
+          <t>-3,79; -0,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,37</t>
+          <t>-0,58; 4,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,9</t>
+          <t>-100,0; 102,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,32; 21,78</t>
+          <t>-93,01; 11,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 416,21</t>
+          <t>-38,95; 434,35</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-12,28%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,83</t>
+          <t>-3,54; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -2,03</t>
+          <t>-6,01; -2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,14</t>
+          <t>-3,22; -0,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 2,74</t>
+          <t>-1,06; 6,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,71</t>
+          <t>-100,0; 249,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 67,13</t>
+          <t>-100,0; 144,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 380,13</t>
+          <t>-68,15; 814,45</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-56,42%</t>
+          <t>-27,94%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,65</t>
+          <t>-0,66; 1,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -0,01</t>
+          <t>-3,75; 0,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,93</t>
+          <t>-0,76; 3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,12</t>
+          <t>-2,4; 1,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-94,59; 20,75</t>
+          <t>-92,6; 55,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 396,11</t>
+          <t>-48,66; 426,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 25,67</t>
+          <t>-78,2; 162,15</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-22,18%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,06</t>
+          <t>-1,32; -0,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,63</t>
+          <t>-2,7; -0,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,33</t>
+          <t>-1,46; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,71</t>
+          <t>-0,75; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-93,63; 7,88</t>
+          <t>-92,11; 2,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-86,29; -24,03</t>
+          <t>-86,71; -28,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 21,08</t>
+          <t>-63,82; 27,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 50,79</t>
+          <t>-36,37; 115,8</t>
         </is>
       </c>
     </row>
